--- a/uploads/data.xlsx
+++ b/uploads/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hapi2999/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hapi2999/Documents/apps/moto/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1A7918-2C80-694E-9EDD-1DCD2237FFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF302055-73A5-204B-97E6-A0B0AF549193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Номер участка</t>
   </si>
@@ -34,16 +34,10 @@
     <t>Долг по целевым взносам</t>
   </si>
   <si>
-    <t>255A</t>
-  </si>
-  <si>
-    <t>350A</t>
-  </si>
-  <si>
-    <t>281A</t>
-  </si>
-  <si>
-    <t>223A</t>
+    <t>200A</t>
+  </si>
+  <si>
+    <t>277A</t>
   </si>
 </sst>
 </file>
@@ -354,8 +348,8 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="1">
-        <v>242</v>
+      <c r="A2" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="1">
         <v>2423</v>
@@ -368,8 +362,8 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1">
-        <v>1</v>
+      <c r="A3" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="B3" s="1">
         <v>234234</v>
@@ -383,98 +377,52 @@
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
-        <v>35</v>
+        <v>375</v>
       </c>
       <c r="B4" s="1">
-        <v>234</v>
+        <v>3242</v>
       </c>
       <c r="C4" s="1">
-        <v>235235</v>
+        <v>23423</v>
       </c>
       <c r="D4" s="1">
-        <v>235</v>
+        <v>32423</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1">
-        <v>45</v>
-      </c>
-      <c r="B5" s="1">
-        <v>532523</v>
-      </c>
-      <c r="C5" s="1">
-        <v>235235</v>
-      </c>
-      <c r="D5" s="1">
-        <v>235235</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
-        <v>211</v>
-      </c>
-      <c r="B6" s="1">
-        <v>235325</v>
-      </c>
-      <c r="C6" s="1">
-        <v>235235</v>
-      </c>
-      <c r="D6" s="1">
-        <v>235325235</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1">
-        <v>11</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1">
-        <v>555</v>
-      </c>
-      <c r="C8" s="1">
-        <v>732</v>
-      </c>
-      <c r="D8" s="1">
-        <v>9999</v>
-      </c>
+      <c r="A8" s="3"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1">
-        <v>394349</v>
-      </c>
-      <c r="C9" s="1">
-        <v>3553535</v>
-      </c>
-      <c r="D9" s="1">
-        <v>3533355</v>
-      </c>
+      <c r="A9" s="3"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1">
-        <v>345346436</v>
-      </c>
-      <c r="C10" s="1">
-        <v>3463463535</v>
-      </c>
-      <c r="D10" s="1">
-        <v>345345345345</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
